--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S541"/>
+  <dimension ref="A1:S548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7853,7 +7853,11 @@
       <c r="O129" t="n">
         <v>39</v>
       </c>
-      <c r="Q129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
     </row>
@@ -8495,21 +8499,25 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M141" t="n">
         <v>150</v>
       </c>
       <c r="N141" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="O141" t="n">
         <v>-3</v>
       </c>
-      <c r="Q141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
@@ -8552,21 +8560,25 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M142" t="n">
         <v>149</v>
       </c>
       <c r="N142" t="n">
-        <v>149</v>
+        <v>298</v>
       </c>
       <c r="O142" t="n">
         <v>-3</v>
       </c>
-      <c r="Q142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
@@ -8667,21 +8679,25 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M144" t="n">
         <v>175</v>
       </c>
       <c r="N144" t="n">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="O144" t="n">
         <v>-21</v>
       </c>
-      <c r="Q144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
@@ -10738,21 +10754,25 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M180" t="n">
         <v>8.25</v>
       </c>
       <c r="N180" t="n">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="O180" t="n">
         <v>36</v>
       </c>
-      <c r="Q180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
     </row>
@@ -15225,21 +15245,25 @@
         <v>0</v>
       </c>
       <c r="K258" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M258" t="n">
         <v>13.69</v>
       </c>
       <c r="N258" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="O258" t="n">
         <v>28</v>
       </c>
-      <c r="Q258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr"/>
     </row>
@@ -31489,6 +31513,448 @@
       </c>
       <c r="R541" t="inlineStr"/>
       <c r="S541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>BlackStack Local 755 IPA 4pk 16oz can</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>869283000400</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Artisan Beer</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>152</v>
+      </c>
+      <c r="F542" t="n">
+        <v>5</v>
+      </c>
+      <c r="G542" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H542" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I542" t="n">
+        <v>42</v>
+      </c>
+      <c r="J542" t="n">
+        <v>37</v>
+      </c>
+      <c r="K542" t="n">
+        <v>6</v>
+      </c>
+      <c r="L542" t="n">
+        <v>1</v>
+      </c>
+      <c r="M542" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="N542" t="n">
+        <v>69</v>
+      </c>
+      <c r="O542" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr"/>
+      <c r="S542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Paulaner Original Munich Lager 4pk 17oz can</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>080157311648</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>73</v>
+      </c>
+      <c r="F543" t="n">
+        <v>6</v>
+      </c>
+      <c r="G543" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H543" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I543" t="n">
+        <v>14</v>
+      </c>
+      <c r="J543" t="n">
+        <v>0</v>
+      </c>
+      <c r="K543" t="n">
+        <v>18</v>
+      </c>
+      <c r="L543" t="n">
+        <v>3</v>
+      </c>
+      <c r="M543" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="N543" t="n">
+        <v>131</v>
+      </c>
+      <c r="O543" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr"/>
+      <c r="S543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Paulaner Oktoberfest Bier 12pk 11oz btl</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>080157114638</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>94</v>
+      </c>
+      <c r="F544" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G544" t="n">
+        <v>174</v>
+      </c>
+      <c r="H544" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I544" t="n">
+        <v>22</v>
+      </c>
+      <c r="J544" t="n">
+        <v>16</v>
+      </c>
+      <c r="K544" t="n">
+        <v>6</v>
+      </c>
+      <c r="L544" t="n">
+        <v>3</v>
+      </c>
+      <c r="M544" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="N544" t="n">
+        <v>82</v>
+      </c>
+      <c r="O544" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr"/>
+      <c r="S544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Paulaner Pils 4pk 17oz can</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>080157344042</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>45</v>
+      </c>
+      <c r="F545" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G545" t="n">
+        <v>2</v>
+      </c>
+      <c r="H545" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I545" t="n">
+        <v>13</v>
+      </c>
+      <c r="J545" t="n">
+        <v>7</v>
+      </c>
+      <c r="K545" t="n">
+        <v>6</v>
+      </c>
+      <c r="L545" t="n">
+        <v>1</v>
+      </c>
+      <c r="M545" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="N545" t="n">
+        <v>48</v>
+      </c>
+      <c r="O545" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr"/>
+      <c r="S545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Paulaner Salvator 6pk 11oz btl</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>080157611878</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>24</v>
+      </c>
+      <c r="F546" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G546" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H546" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I546" t="n">
+        <v>3</v>
+      </c>
+      <c r="J546" t="n">
+        <v>0</v>
+      </c>
+      <c r="K546" t="n">
+        <v>4</v>
+      </c>
+      <c r="L546" t="n">
+        <v>1</v>
+      </c>
+      <c r="M546" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="N546" t="n">
+        <v>42</v>
+      </c>
+      <c r="O546" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr"/>
+      <c r="S546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Paulaner Grapefruit Radler 4pk 17oz can</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>080157132045</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>68</v>
+      </c>
+      <c r="F547" t="n">
+        <v>10</v>
+      </c>
+      <c r="G547" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H547" t="n">
+        <v>5</v>
+      </c>
+      <c r="I547" t="n">
+        <v>5</v>
+      </c>
+      <c r="J547" t="n">
+        <v>0</v>
+      </c>
+      <c r="K547" t="n">
+        <v>6</v>
+      </c>
+      <c r="L547" t="n">
+        <v>1</v>
+      </c>
+      <c r="M547" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="N547" t="n">
+        <v>49</v>
+      </c>
+      <c r="O547" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr"/>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Paulaner Oktoberfest Marzen 12pk 11oz btl</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>080157030440</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>93</v>
+      </c>
+      <c r="F548" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G548" t="n">
+        <v>57</v>
+      </c>
+      <c r="H548" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I548" t="n">
+        <v>5</v>
+      </c>
+      <c r="J548" t="n">
+        <v>0</v>
+      </c>
+      <c r="K548" t="n">
+        <v>6</v>
+      </c>
+      <c r="L548" t="n">
+        <v>3</v>
+      </c>
+      <c r="M548" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="N548" t="n">
+        <v>82</v>
+      </c>
+      <c r="O548" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr"/>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31501,7 +31967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33070,21 +33536,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>150</v>
       </c>
       <c r="N26" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="O26" t="n">
         <v>-3</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
@@ -33127,21 +33597,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>149</v>
       </c>
       <c r="N27" t="n">
-        <v>149</v>
+        <v>298</v>
       </c>
       <c r="O27" t="n">
         <v>-3</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
@@ -33189,21 +33663,25 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>175</v>
       </c>
       <c r="N28" t="n">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="O28" t="n">
         <v>-21</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
@@ -34743,6 +35221,138 @@
       <c r="S53" t="inlineStr">
         <is>
           <t>Seasonal - last year ~24/wk vs 14 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Paulaner Grapefruit Radler 4pk 17oz can</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>080157132045</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>68</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="N54" t="n">
+        <v>49</v>
+      </c>
+      <c r="O54" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Paulaner Oktoberfest Marzen 12pk 11oz btl</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>080157030440</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hohensteins, Inc.</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>93</v>
+      </c>
+      <c r="F55" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G55" t="n">
+        <v>57</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="N55" t="n">
+        <v>82</v>
+      </c>
+      <c r="O55" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19872,25 +19872,21 @@
         <v>12</v>
       </c>
       <c r="K339" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="L339" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M339" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="N339" t="n">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="O339" t="n">
         <v>35</v>
       </c>
-      <c r="Q339" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q339" t="inlineStr"/>
       <c r="R339" t="inlineStr"/>
       <c r="S339" t="inlineStr"/>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29089,119 +29089,119 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
+          <t>Lupulin Hooey IPA 4pk 16oz can</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>857492006092</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>152</v>
+      </c>
+      <c r="F503" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G503" t="n">
+        <v>12</v>
+      </c>
+      <c r="H503" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="I503" t="n">
+        <v>60</v>
+      </c>
+      <c r="J503" t="n">
+        <v>52</v>
+      </c>
+      <c r="K503" t="n">
+        <v>12</v>
+      </c>
+      <c r="L503" t="n">
+        <v>2</v>
+      </c>
+      <c r="M503" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="N503" t="n">
+        <v>132</v>
+      </c>
+      <c r="O503" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr"/>
+      <c r="S503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
           <t xml:space="preserve">Firestone Walker Cali Squeeze Blood Orange
 12pk 12oz can
 </t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>602755011630</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
+      <c r="C504" t="inlineStr">
         <is>
           <t>Craft</t>
         </is>
       </c>
-      <c r="E503" t="n">
+      <c r="E504" t="n">
         <v>9</v>
       </c>
-      <c r="F503" t="n">
+      <c r="F504" t="n">
         <v>4.8</v>
       </c>
-      <c r="G503" t="n">
+      <c r="G504" t="n">
         <v>14</v>
       </c>
-      <c r="H503" t="n">
-        <v>0</v>
-      </c>
-      <c r="I503" t="n">
+      <c r="H504" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" t="n">
         <v>2</v>
       </c>
-      <c r="J503" t="n">
-        <v>0</v>
-      </c>
-      <c r="K503" t="n">
+      <c r="J504" t="n">
+        <v>0</v>
+      </c>
+      <c r="K504" t="n">
         <v>2</v>
       </c>
-      <c r="L503" t="n">
+      <c r="L504" t="n">
         <v>2</v>
       </c>
-      <c r="M503" t="n">
+      <c r="M504" t="n">
         <v>15.02</v>
       </c>
-      <c r="N503" t="n">
+      <c r="N504" t="n">
         <v>30</v>
       </c>
-      <c r="O503" t="n">
+      <c r="O504" t="n">
         <v>14</v>
       </c>
-      <c r="Q503" t="inlineStr">
+      <c r="Q504" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R503" t="inlineStr"/>
-      <c r="S503" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>Carbliss Peach 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>86000981953</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>College City Beverage, Inc.</t>
-        </is>
-      </c>
-      <c r="E504" t="n">
-        <v>168</v>
-      </c>
-      <c r="F504" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G504" t="n">
-        <v>-11</v>
-      </c>
-      <c r="H504" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="I504" t="n">
-        <v>23</v>
-      </c>
-      <c r="J504" t="n">
-        <v>20</v>
-      </c>
-      <c r="K504" t="n">
-        <v>6</v>
-      </c>
-      <c r="L504" t="n">
-        <v>1</v>
-      </c>
-      <c r="M504" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="N504" t="n">
-        <v>53</v>
-      </c>
-      <c r="O504" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q504" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R504" t="inlineStr"/>
